--- a/artfynd/A 52683-2022 artfynd.xlsx
+++ b/artfynd/A 52683-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121559531</v>
       </c>
       <c r="B2" t="n">
-        <v>105194</v>
+        <v>105195</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>121559520</v>
       </c>
       <c r="B3" t="n">
-        <v>57783</v>
+        <v>57784</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 52683-2022 artfynd.xlsx
+++ b/artfynd/A 52683-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121559531</v>
+        <v>121559520</v>
       </c>
       <c r="B2" t="n">
-        <v>105195</v>
+        <v>57785</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221725</v>
+        <v>103001</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>691029</v>
+        <v>691117</v>
       </c>
       <c r="R2" t="n">
-        <v>7127936</v>
+        <v>7127938</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121559520</v>
+        <v>121559531</v>
       </c>
       <c r="B3" t="n">
-        <v>57784</v>
+        <v>105203</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103001</v>
+        <v>221725</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>691117</v>
+        <v>691029</v>
       </c>
       <c r="R3" t="n">
-        <v>7127938</v>
+        <v>7127936</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 52683-2022 artfynd.xlsx
+++ b/artfynd/A 52683-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121559531</v>
+        <v>121559520</v>
       </c>
       <c r="B2" t="n">
-        <v>105203</v>
+        <v>57785</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221725</v>
+        <v>103001</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>691029</v>
+        <v>691117</v>
       </c>
       <c r="R2" t="n">
-        <v>7127936</v>
+        <v>7127938</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121559520</v>
+        <v>121559531</v>
       </c>
       <c r="B3" t="n">
-        <v>57785</v>
+        <v>105203</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103001</v>
+        <v>221725</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>691117</v>
+        <v>691029</v>
       </c>
       <c r="R3" t="n">
-        <v>7127938</v>
+        <v>7127936</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
